--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/121.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/121.xlsx
@@ -426,13 +426,13 @@
         <v>-7.163551784889121</v>
       </c>
       <c r="E2">
-        <v>-21.39644853285504</v>
+        <v>-20.65004280454077</v>
       </c>
       <c r="F2">
-        <v>1.047762847285655</v>
+        <v>0.6866352496678081</v>
       </c>
       <c r="G2">
-        <v>-14.13154585891484</v>
+        <v>-13.17042848644087</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.896044963842852</v>
       </c>
       <c r="E3">
-        <v>-21.59472323880687</v>
+        <v>-20.48561844179627</v>
       </c>
       <c r="F3">
-        <v>1.20855227363865</v>
+        <v>1.580648284036966</v>
       </c>
       <c r="G3">
-        <v>-14.20374913933042</v>
+        <v>-12.26663569522118</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.519505091408397</v>
       </c>
       <c r="E4">
-        <v>-21.60064648280891</v>
+        <v>-20.52660113156568</v>
       </c>
       <c r="F4">
-        <v>0.7726752866943843</v>
+        <v>1.465521782395891</v>
       </c>
       <c r="G4">
-        <v>-13.49156164046373</v>
+        <v>-11.42581282694879</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.069894544130007</v>
       </c>
       <c r="E5">
-        <v>-22.52110410960799</v>
+        <v>-19.70265434281808</v>
       </c>
       <c r="F5">
-        <v>1.306170401854156</v>
+        <v>0.8772898059939339</v>
       </c>
       <c r="G5">
-        <v>-13.21398998386406</v>
+        <v>-11.55078143126181</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.571843066110155</v>
       </c>
       <c r="E6">
-        <v>-22.45361626147167</v>
+        <v>-21.46899921493192</v>
       </c>
       <c r="F6">
-        <v>1.073629447805473</v>
+        <v>0.9995402672990849</v>
       </c>
       <c r="G6">
-        <v>-12.92030752940752</v>
+        <v>-11.53753842104789</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.05797961984578</v>
       </c>
       <c r="E7">
-        <v>-24.23326579022006</v>
+        <v>-22.39996290142879</v>
       </c>
       <c r="F7">
-        <v>1.037073594319931</v>
+        <v>1.513911692597827</v>
       </c>
       <c r="G7">
-        <v>-12.54654030034961</v>
+        <v>-10.58155780092523</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.550829926439231</v>
       </c>
       <c r="E8">
-        <v>-23.60066967066656</v>
+        <v>-22.3572186352704</v>
       </c>
       <c r="F8">
-        <v>1.027477786325901</v>
+        <v>1.800786921330935</v>
       </c>
       <c r="G8">
-        <v>-11.8204945622266</v>
+        <v>-10.71875223676873</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.080453490711518</v>
       </c>
       <c r="E9">
-        <v>-23.85294190068586</v>
+        <v>-23.2601601246078</v>
       </c>
       <c r="F9">
-        <v>1.108280056264576</v>
+        <v>1.06936169894625</v>
       </c>
       <c r="G9">
-        <v>-11.4890255602915</v>
+        <v>-10.24800522329988</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.662493835935006</v>
       </c>
       <c r="E10">
-        <v>-25.26885986866415</v>
+        <v>-23.61105346156615</v>
       </c>
       <c r="F10">
-        <v>1.268469744617944</v>
+        <v>1.579528331308381</v>
       </c>
       <c r="G10">
-        <v>-11.28577685323481</v>
+        <v>-10.80813599326956</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.312491598272939</v>
       </c>
       <c r="E11">
-        <v>-24.63340628201182</v>
+        <v>-23.78858322808885</v>
       </c>
       <c r="F11">
-        <v>1.605575515922009</v>
+        <v>2.240469428123662</v>
       </c>
       <c r="G11">
-        <v>-11.10619231606484</v>
+        <v>-10.86569190064378</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.037888235746623</v>
       </c>
       <c r="E12">
-        <v>-26.04642149815119</v>
+        <v>-24.5607197457147</v>
       </c>
       <c r="F12">
-        <v>1.430100792252184</v>
+        <v>1.83393487132136</v>
       </c>
       <c r="G12">
-        <v>-9.70853958671157</v>
+        <v>-9.38454520748888</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.832273228916142</v>
       </c>
       <c r="E13">
-        <v>-27.39808494843464</v>
+        <v>-26.26621098411347</v>
       </c>
       <c r="F13">
-        <v>1.802861153307545</v>
+        <v>1.706253633323455</v>
       </c>
       <c r="G13">
-        <v>-10.60446072741015</v>
+        <v>-9.577248068453509</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.691858357109018</v>
       </c>
       <c r="E14">
-        <v>-28.7903054119308</v>
+        <v>-26.30554530934409</v>
       </c>
       <c r="F14">
-        <v>1.991265035400264</v>
+        <v>2.655728350412248</v>
       </c>
       <c r="G14">
-        <v>-9.70121918141245</v>
+        <v>-8.004821072736412</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.599926443661066</v>
       </c>
       <c r="E15">
-        <v>-28.76980048162407</v>
+        <v>-28.26627039976318</v>
       </c>
       <c r="F15">
-        <v>2.326394322081249</v>
+        <v>2.510132838961402</v>
       </c>
       <c r="G15">
-        <v>-9.87458252250571</v>
+        <v>-8.19599488445434</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.540331410200165</v>
       </c>
       <c r="E16">
-        <v>-29.29405286054405</v>
+        <v>-27.53625321888267</v>
       </c>
       <c r="F16">
-        <v>2.804017712656999</v>
+        <v>2.942197679117985</v>
       </c>
       <c r="G16">
-        <v>-9.728184260187966</v>
+        <v>-8.56844634366691</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.498411366172206</v>
       </c>
       <c r="E17">
-        <v>-30.34643852060859</v>
+        <v>-28.2476221437996</v>
       </c>
       <c r="F17">
-        <v>2.539008069888187</v>
+        <v>3.431903636630969</v>
       </c>
       <c r="G17">
-        <v>-8.99632419746162</v>
+        <v>-7.958112883837717</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.454397417936919</v>
       </c>
       <c r="E18">
-        <v>-32.00649105081439</v>
+        <v>-29.96649955136504</v>
       </c>
       <c r="F18">
-        <v>2.928836112910829</v>
+        <v>3.40722325823196</v>
       </c>
       <c r="G18">
-        <v>-8.935519880743549</v>
+        <v>-8.482550525683765</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.396068751525809</v>
       </c>
       <c r="E19">
-        <v>-31.42873927996779</v>
+        <v>-30.41914769927574</v>
       </c>
       <c r="F19">
-        <v>2.936862993043956</v>
+        <v>3.630203195717531</v>
       </c>
       <c r="G19">
-        <v>-8.566772920671593</v>
+        <v>-8.844833479283617</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.306890468346977</v>
       </c>
       <c r="E20">
-        <v>-32.97184170468851</v>
+        <v>-29.64308499468524</v>
       </c>
       <c r="F20">
-        <v>3.518839138819971</v>
+        <v>4.066409872888111</v>
       </c>
       <c r="G20">
-        <v>-8.471115468549101</v>
+        <v>-7.625734983530645</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.173030595852615</v>
       </c>
       <c r="E21">
-        <v>-32.87217225601669</v>
+        <v>-31.67228514057431</v>
       </c>
       <c r="F21">
-        <v>3.600852481901539</v>
+        <v>4.02809953724344</v>
       </c>
       <c r="G21">
-        <v>-9.778521480131408</v>
+        <v>-8.155776951800226</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.986842031278471</v>
       </c>
       <c r="E22">
-        <v>-34.20682675792733</v>
+        <v>-31.40995516978398</v>
       </c>
       <c r="F22">
-        <v>3.628284696812647</v>
+        <v>3.532101300938791</v>
       </c>
       <c r="G22">
-        <v>-8.864297685574241</v>
+        <v>-7.207097049647332</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.739558611035351</v>
       </c>
       <c r="E23">
-        <v>-33.30528456705829</v>
+        <v>-32.97457463875214</v>
       </c>
       <c r="F23">
-        <v>3.879190556181395</v>
+        <v>4.630947228100391</v>
       </c>
       <c r="G23">
-        <v>-9.122775913919499</v>
+        <v>-7.909380181236844</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.433422753751078</v>
       </c>
       <c r="E24">
-        <v>-34.13556895517964</v>
+        <v>-32.59548928685904</v>
       </c>
       <c r="F24">
-        <v>4.190807462501319</v>
+        <v>4.322711717518695</v>
       </c>
       <c r="G24">
-        <v>-8.82365975656052</v>
+        <v>-6.877800216384579</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.073132880485865</v>
       </c>
       <c r="E25">
-        <v>-33.39802997897239</v>
+        <v>-34.26420025936751</v>
       </c>
       <c r="F25">
-        <v>3.716348435404263</v>
+        <v>4.51648176364675</v>
       </c>
       <c r="G25">
-        <v>-8.723785934734142</v>
+        <v>-7.159266682975306</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.6688006955230287</v>
       </c>
       <c r="E26">
-        <v>-34.54896202615485</v>
+        <v>-34.40168925871439</v>
       </c>
       <c r="F26">
-        <v>3.491971870477572</v>
+        <v>4.92503090997266</v>
       </c>
       <c r="G26">
-        <v>-8.255808272261458</v>
+        <v>-7.655561287505998</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.2404352444299254</v>
       </c>
       <c r="E27">
-        <v>-33.88533227422678</v>
+        <v>-33.17898995545838</v>
       </c>
       <c r="F27">
-        <v>3.887752561656731</v>
+        <v>4.549457413217393</v>
       </c>
       <c r="G27">
-        <v>-8.732684607603355</v>
+        <v>-6.966304605507482</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.1945691199205555</v>
       </c>
       <c r="E28">
-        <v>-33.0455131840823</v>
+        <v>-33.87498244688226</v>
       </c>
       <c r="F28">
-        <v>3.597114888180108</v>
+        <v>4.77870643520735</v>
       </c>
       <c r="G28">
-        <v>-8.380511097628155</v>
+        <v>-6.756490174110349</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.6133899089277679</v>
       </c>
       <c r="E29">
-        <v>-33.98349826952806</v>
+        <v>-32.64542703397863</v>
       </c>
       <c r="F29">
-        <v>3.495439416425691</v>
+        <v>4.120894910439846</v>
       </c>
       <c r="G29">
-        <v>-8.431757215943561</v>
+        <v>-6.961540271803168</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.995606031526972</v>
       </c>
       <c r="E30">
-        <v>-32.56672215572532</v>
+        <v>-33.17177609636416</v>
       </c>
       <c r="F30">
-        <v>3.329973027716489</v>
+        <v>4.253627532860022</v>
       </c>
       <c r="G30">
-        <v>-8.306637675438816</v>
+        <v>-6.138370375520593</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.326582136162325</v>
       </c>
       <c r="E31">
-        <v>-33.53752282806767</v>
+        <v>-33.5939861062323</v>
       </c>
       <c r="F31">
-        <v>3.420945992626736</v>
+        <v>4.242325288016225</v>
       </c>
       <c r="G31">
-        <v>-7.70098979999651</v>
+        <v>-7.117601731613477</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.591016419040757</v>
       </c>
       <c r="E32">
-        <v>-33.07433465690411</v>
+        <v>-31.95979342684729</v>
       </c>
       <c r="F32">
-        <v>2.981460637275876</v>
+        <v>3.615741557599457</v>
       </c>
       <c r="G32">
-        <v>-7.417088667008675</v>
+        <v>-6.311080753523526</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.784025455871204</v>
       </c>
       <c r="E33">
-        <v>-32.61080005747898</v>
+        <v>-31.51824004025539</v>
       </c>
       <c r="F33">
-        <v>2.977472876598799</v>
+        <v>3.968438860159014</v>
       </c>
       <c r="G33">
-        <v>-7.524699609272224</v>
+        <v>-6.834645590434762</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.904129407971329</v>
       </c>
       <c r="E34">
-        <v>-32.66564214194887</v>
+        <v>-30.69069537890869</v>
       </c>
       <c r="F34">
-        <v>2.930961703666412</v>
+        <v>4.013178983584215</v>
       </c>
       <c r="G34">
-        <v>-8.074645467521396</v>
+        <v>-6.793817350570592</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.954632915070462</v>
       </c>
       <c r="E35">
-        <v>-31.667971769082</v>
+        <v>-30.88557146511777</v>
       </c>
       <c r="F35">
-        <v>2.964336626325204</v>
+        <v>3.99475774928076</v>
       </c>
       <c r="G35">
-        <v>-7.454323969265253</v>
+        <v>-6.98799676123697</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.946611575558572</v>
       </c>
       <c r="E36">
-        <v>-31.88665857162342</v>
+        <v>-30.84092071140214</v>
       </c>
       <c r="F36">
-        <v>3.026808782374732</v>
+        <v>3.950831082645108</v>
       </c>
       <c r="G36">
-        <v>-7.875504849857137</v>
+        <v>-6.360528762424358</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.891652068414644</v>
       </c>
       <c r="E37">
-        <v>-31.56803740468074</v>
+        <v>-31.06611945956659</v>
       </c>
       <c r="F37">
-        <v>3.12659391971596</v>
+        <v>4.099022697536328</v>
       </c>
       <c r="G37">
-        <v>-7.64939915341736</v>
+        <v>-5.613391332117236</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.807743989427862</v>
       </c>
       <c r="E38">
-        <v>-29.7586018381469</v>
+        <v>-28.85883933756288</v>
       </c>
       <c r="F38">
-        <v>3.299595138321026</v>
+        <v>3.821738306592833</v>
       </c>
       <c r="G38">
-        <v>-7.232805420565581</v>
+        <v>-6.220154822889753</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.71280161911136</v>
       </c>
       <c r="E39">
-        <v>-29.9551421385538</v>
+        <v>-28.48261824547964</v>
       </c>
       <c r="F39">
-        <v>3.17940565511404</v>
+        <v>3.896682362258909</v>
       </c>
       <c r="G39">
-        <v>-7.401109118014179</v>
+        <v>-7.535101081615664</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.623900068861601</v>
       </c>
       <c r="E40">
-        <v>-29.83715954099496</v>
+        <v>-28.15775910559138</v>
       </c>
       <c r="F40">
-        <v>3.064701620848393</v>
+        <v>4.258881038928577</v>
       </c>
       <c r="G40">
-        <v>-7.695401879680776</v>
+        <v>-6.585732122935286</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.557013136996904</v>
       </c>
       <c r="E41">
-        <v>-29.99128162537202</v>
+        <v>-28.00330644261177</v>
       </c>
       <c r="F41">
-        <v>3.335428655431327</v>
+        <v>3.683208769087865</v>
       </c>
       <c r="G41">
-        <v>-7.640208451829356</v>
+        <v>-7.839815002955056</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.52156941587448</v>
       </c>
       <c r="E42">
-        <v>-29.42647223323934</v>
+        <v>-26.59524537703679</v>
       </c>
       <c r="F42">
-        <v>3.298109047200403</v>
+        <v>3.780994227518736</v>
       </c>
       <c r="G42">
-        <v>-7.993618982332468</v>
+        <v>-7.52383336678053</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.522845823471749</v>
       </c>
       <c r="E43">
-        <v>-27.27614672883011</v>
+        <v>-27.16071592637459</v>
       </c>
       <c r="F43">
-        <v>3.241937453616569</v>
+        <v>4.226970669837934</v>
       </c>
       <c r="G43">
-        <v>-7.985776862805396</v>
+        <v>-7.874717356682869</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.558422023116545</v>
       </c>
       <c r="E44">
-        <v>-27.68164893384695</v>
+        <v>-26.80005919945571</v>
       </c>
       <c r="F44">
-        <v>3.330471704892974</v>
+        <v>3.435334734413364</v>
       </c>
       <c r="G44">
-        <v>-7.849438825788908</v>
+        <v>-7.592689801205478</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.622156599309007</v>
       </c>
       <c r="E45">
-        <v>-27.48435237828076</v>
+        <v>-27.66123910149438</v>
       </c>
       <c r="F45">
-        <v>3.305950373035304</v>
+        <v>3.515133023059846</v>
       </c>
       <c r="G45">
-        <v>-8.592471447925163</v>
+        <v>-6.640659771840391</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.704689259024677</v>
       </c>
       <c r="E46">
-        <v>-26.63108372033349</v>
+        <v>-24.46280960919486</v>
       </c>
       <c r="F46">
-        <v>3.394564147582378</v>
+        <v>4.293816605774243</v>
       </c>
       <c r="G46">
-        <v>-8.280043374699517</v>
+        <v>-6.624335694582153</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.793669686879561</v>
       </c>
       <c r="E47">
-        <v>-26.52649861312635</v>
+        <v>-26.47822960867859</v>
       </c>
       <c r="F47">
-        <v>3.291309807558225</v>
+        <v>3.848600604730815</v>
       </c>
       <c r="G47">
-        <v>-8.320700991042596</v>
+        <v>-7.083116093023714</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.877239879619275</v>
       </c>
       <c r="E48">
-        <v>-25.78056384610888</v>
+        <v>-25.33574995823145</v>
       </c>
       <c r="F48">
-        <v>3.392536304180325</v>
+        <v>4.611787090073639</v>
       </c>
       <c r="G48">
-        <v>-8.362405317063137</v>
+        <v>-7.23766162847356</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.942603463831273</v>
       </c>
       <c r="E49">
-        <v>-25.75121933453917</v>
+        <v>-23.09700373458545</v>
       </c>
       <c r="F49">
-        <v>3.52421524326414</v>
+        <v>4.357077367591235</v>
       </c>
       <c r="G49">
-        <v>-8.224561199350866</v>
+        <v>-8.304705035940303</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.980125336382116</v>
       </c>
       <c r="E50">
-        <v>-24.69074129142293</v>
+        <v>-23.39017714184203</v>
       </c>
       <c r="F50">
-        <v>3.348641115505979</v>
+        <v>4.372518135979418</v>
       </c>
       <c r="G50">
-        <v>-8.972961899958372</v>
+        <v>-9.286623712490371</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.983204318689842</v>
       </c>
       <c r="E51">
-        <v>-23.85705828355883</v>
+        <v>-22.155665314137</v>
       </c>
       <c r="F51">
-        <v>3.601057917017433</v>
+        <v>4.001957918745893</v>
       </c>
       <c r="G51">
-        <v>-9.179071832214893</v>
+        <v>-8.113491849563662</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.947600029922047</v>
       </c>
       <c r="E52">
-        <v>-23.79293509161022</v>
+        <v>-23.2302269114171</v>
       </c>
       <c r="F52">
-        <v>3.732312731991015</v>
+        <v>4.185495970714569</v>
       </c>
       <c r="G52">
-        <v>-8.877635851213386</v>
+        <v>-8.120638350120132</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.873919319573695</v>
       </c>
       <c r="E53">
-        <v>-23.2949931466748</v>
+        <v>-21.95451502719029</v>
       </c>
       <c r="F53">
-        <v>3.572421255902654</v>
+        <v>4.053093038520706</v>
       </c>
       <c r="G53">
-        <v>-9.529220828487917</v>
+        <v>-7.918771037339974</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.763152598162105</v>
       </c>
       <c r="E54">
-        <v>-22.73309103485505</v>
+        <v>-21.24760664917093</v>
       </c>
       <c r="F54">
-        <v>3.377743319101131</v>
+        <v>3.843499518264375</v>
       </c>
       <c r="G54">
-        <v>-9.615343050758662</v>
+        <v>-7.414276660132231</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.619626219634401</v>
       </c>
       <c r="E55">
-        <v>-22.82850598219666</v>
+        <v>-21.64966721394194</v>
       </c>
       <c r="F55">
-        <v>3.540640112126848</v>
+        <v>3.908044249555708</v>
       </c>
       <c r="G55">
-        <v>-9.512844251684728</v>
+        <v>-8.020423281251572</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.447603870210231</v>
       </c>
       <c r="E56">
-        <v>-21.91451954475455</v>
+        <v>-21.02984139109007</v>
       </c>
       <c r="F56">
-        <v>3.582784132111676</v>
+        <v>4.111872332688554</v>
       </c>
       <c r="G56">
-        <v>-10.24120325100715</v>
+        <v>-8.202997011262195</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.249936268040914</v>
       </c>
       <c r="E57">
-        <v>-21.93705323141672</v>
+        <v>-21.70564368115075</v>
       </c>
       <c r="F57">
-        <v>3.186904036844181</v>
+        <v>3.757973897394938</v>
       </c>
       <c r="G57">
-        <v>-9.936594328757657</v>
+        <v>-8.311946691921998</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.032915086961494</v>
       </c>
       <c r="E58">
-        <v>-20.03611305484689</v>
+        <v>-19.5144509630593</v>
       </c>
       <c r="F58">
-        <v>3.277032067003573</v>
+        <v>4.083504062612282</v>
       </c>
       <c r="G58">
-        <v>-10.06643226586488</v>
+        <v>-9.258155834240629</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.798832137244714</v>
       </c>
       <c r="E59">
-        <v>-21.05383777485672</v>
+        <v>-19.17375122109222</v>
       </c>
       <c r="F59">
-        <v>3.319943155203393</v>
+        <v>4.349716494849959</v>
       </c>
       <c r="G59">
-        <v>-10.06505415280992</v>
+        <v>-8.408171795374273</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.5523804670953396</v>
       </c>
       <c r="E60">
-        <v>-20.06863202669597</v>
+        <v>-18.72619307796614</v>
       </c>
       <c r="F60">
-        <v>3.233635555505712</v>
+        <v>3.80484789524975</v>
       </c>
       <c r="G60">
-        <v>-10.16079691669295</v>
+        <v>-8.201002028554052</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.297964674139433</v>
       </c>
       <c r="E61">
-        <v>-19.86925690156027</v>
+        <v>-18.97065821879622</v>
       </c>
       <c r="F61">
-        <v>2.876506487341178</v>
+        <v>3.611632855281572</v>
       </c>
       <c r="G61">
-        <v>-10.53084980294557</v>
+        <v>-8.659126182683723</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.03767279993668087</v>
       </c>
       <c r="E62">
-        <v>-19.94212457681769</v>
+        <v>-18.69726518600514</v>
       </c>
       <c r="F62">
-        <v>3.014741126050748</v>
+        <v>3.706060112261493</v>
       </c>
       <c r="G62">
-        <v>-10.04396902306893</v>
+        <v>-9.448132000089359</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.2212601364777644</v>
       </c>
       <c r="E63">
-        <v>-18.70616363743022</v>
+        <v>-17.96423204143553</v>
       </c>
       <c r="F63">
-        <v>3.251718815908826</v>
+        <v>3.762713815673757</v>
       </c>
       <c r="G63">
-        <v>-10.53911848127537</v>
+        <v>-10.04404449116479</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.4750492954085188</v>
       </c>
       <c r="E64">
-        <v>-18.54016336573104</v>
+        <v>-18.14545251427448</v>
       </c>
       <c r="F64">
-        <v>2.942926642432448</v>
+        <v>4.02818237398372</v>
       </c>
       <c r="G64">
-        <v>-10.30115773134132</v>
+        <v>-8.860212564732734</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.7178530998993705</v>
       </c>
       <c r="E65">
-        <v>-19.30320217907548</v>
+        <v>-16.92266943424932</v>
       </c>
       <c r="F65">
-        <v>2.672002456407648</v>
+        <v>3.794412122709283</v>
       </c>
       <c r="G65">
-        <v>-10.45215298506385</v>
+        <v>-9.550847359786216</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.9418855628593719</v>
       </c>
       <c r="E66">
-        <v>-18.70250463043202</v>
+        <v>-18.05831108894488</v>
       </c>
       <c r="F66">
-        <v>2.811607214801448</v>
+        <v>3.491937079046654</v>
       </c>
       <c r="G66">
-        <v>-10.67632276078355</v>
+        <v>-9.282532029205743</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.141940432997544</v>
       </c>
       <c r="E67">
-        <v>-18.14689256900892</v>
+        <v>-18.43752097387319</v>
       </c>
       <c r="F67">
-        <v>2.820190757829257</v>
+        <v>2.985637265720791</v>
       </c>
       <c r="G67">
-        <v>-10.65977227923771</v>
+        <v>-9.412704650912035</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.309966747123815</v>
       </c>
       <c r="E68">
-        <v>-17.95845823707575</v>
+        <v>-16.60487924228705</v>
       </c>
       <c r="F68">
-        <v>2.497992286305972</v>
+        <v>3.105023232547061</v>
       </c>
       <c r="G68">
-        <v>-11.03466496729051</v>
+        <v>-9.525460548580792</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.439361978942541</v>
       </c>
       <c r="E69">
-        <v>-17.35906488894649</v>
+        <v>-17.40253823942012</v>
       </c>
       <c r="F69">
-        <v>2.538567378429898</v>
+        <v>3.475681197134117</v>
       </c>
       <c r="G69">
-        <v>-10.53716287322594</v>
+        <v>-9.024024269866452</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.523853581955682</v>
       </c>
       <c r="E70">
-        <v>-18.54765799021374</v>
+        <v>-17.77241041094462</v>
       </c>
       <c r="F70">
-        <v>2.537535232646009</v>
+        <v>2.678377571939592</v>
       </c>
       <c r="G70">
-        <v>-10.2279864905657</v>
+        <v>-9.128534457756325</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.557210660106177</v>
       </c>
       <c r="E71">
-        <v>-18.09828845748459</v>
+        <v>-17.12064978939066</v>
       </c>
       <c r="F71">
-        <v>2.032444835728233</v>
+        <v>2.996611477073079</v>
       </c>
       <c r="G71">
-        <v>-10.02985648914175</v>
+        <v>-8.746665892668149</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.534314895478995</v>
       </c>
       <c r="E72">
-        <v>-18.24656881039175</v>
+        <v>-16.45043563625545</v>
       </c>
       <c r="F72">
-        <v>2.15223504584707</v>
+        <v>2.800089594432924</v>
       </c>
       <c r="G72">
-        <v>-10.41118365267262</v>
+        <v>-10.66273850352745</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.452457002503277</v>
       </c>
       <c r="E73">
-        <v>-18.47361744018833</v>
+        <v>-16.41878613141584</v>
       </c>
       <c r="F73">
-        <v>1.937164360323429</v>
+        <v>2.35781595440424</v>
       </c>
       <c r="G73">
-        <v>-10.16895731471129</v>
+        <v>-9.693071908280348</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.310009550278295</v>
       </c>
       <c r="E74">
-        <v>-17.65377344889167</v>
+        <v>-16.98034407921101</v>
       </c>
       <c r="F74">
-        <v>2.149945438345732</v>
+        <v>2.535376507194314</v>
       </c>
       <c r="G74">
-        <v>-9.594234952466755</v>
+        <v>-9.86194325705873</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.106402474298863</v>
       </c>
       <c r="E75">
-        <v>-17.27404278945248</v>
+        <v>-17.01574768900298</v>
       </c>
       <c r="F75">
-        <v>2.127912522166071</v>
+        <v>2.694837232233219</v>
       </c>
       <c r="G75">
-        <v>-9.82666684407314</v>
+        <v>-10.01312225918859</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.8467491571832775</v>
       </c>
       <c r="E76">
-        <v>-18.65879579930998</v>
+        <v>-16.84878738081418</v>
       </c>
       <c r="F76">
-        <v>1.857339563920057</v>
+        <v>1.72822856378492</v>
       </c>
       <c r="G76">
-        <v>-9.581615374349131</v>
+        <v>-9.21561151550087</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.5332279628395316</v>
       </c>
       <c r="E77">
-        <v>-18.67580474768279</v>
+        <v>-17.61094314172712</v>
       </c>
       <c r="F77">
-        <v>1.757027584910648</v>
+        <v>2.488118146864602</v>
       </c>
       <c r="G77">
-        <v>-9.081396428833342</v>
+        <v>-7.240801757505948</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.1729488281019473</v>
       </c>
       <c r="E78">
-        <v>-18.63178345185423</v>
+        <v>-16.37543504974041</v>
       </c>
       <c r="F78">
-        <v>1.628125333361017</v>
+        <v>1.672186195515923</v>
       </c>
       <c r="G78">
-        <v>-9.278994872364663</v>
+        <v>-8.40169138279437</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.2248629776524288</v>
       </c>
       <c r="E79">
-        <v>-19.21871443951438</v>
+        <v>-18.85352923858783</v>
       </c>
       <c r="F79">
-        <v>1.674389652807369</v>
+        <v>2.123601698201902</v>
       </c>
       <c r="G79">
-        <v>-8.892558846865739</v>
+        <v>-8.708652940901983</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.6546056075767196</v>
       </c>
       <c r="E80">
-        <v>-20.24289676345914</v>
+        <v>-17.37118761386503</v>
       </c>
       <c r="F80">
-        <v>1.793676215545304</v>
+        <v>1.788677846636812</v>
       </c>
       <c r="G80">
-        <v>-8.49983600085892</v>
+        <v>-7.845586671678119</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.102191687748547</v>
       </c>
       <c r="E81">
-        <v>-19.5543649329629</v>
+        <v>-19.55363584864767</v>
       </c>
       <c r="F81">
-        <v>1.491615355584075</v>
+        <v>2.552956120216525</v>
       </c>
       <c r="G81">
-        <v>-8.1445814238394</v>
+        <v>-7.344501483670639</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.559767578474078</v>
       </c>
       <c r="E82">
-        <v>-20.10359184603519</v>
+        <v>-20.65669966133204</v>
       </c>
       <c r="F82">
-        <v>1.181868902859673</v>
+        <v>1.52080702285873</v>
       </c>
       <c r="G82">
-        <v>-8.543728901659613</v>
+        <v>-6.589800837668998</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.017178256455194</v>
       </c>
       <c r="E83">
-        <v>-20.65516903711745</v>
+        <v>-19.72317285854683</v>
       </c>
       <c r="F83">
-        <v>1.366666073280603</v>
+        <v>1.933133524541406</v>
       </c>
       <c r="G83">
-        <v>-8.345795773529229</v>
+        <v>-8.108045021774984</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.459954773280819</v>
       </c>
       <c r="E84">
-        <v>-22.02966052487357</v>
+        <v>-20.36453610377918</v>
       </c>
       <c r="F84">
-        <v>1.241473250960708</v>
+        <v>1.9976964799156</v>
       </c>
       <c r="G84">
-        <v>-7.348255201134643</v>
+        <v>-7.230879343510187</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.881112001018499</v>
       </c>
       <c r="E85">
-        <v>-22.68728552026746</v>
+        <v>-21.52039286644498</v>
       </c>
       <c r="F85">
-        <v>1.583802707106827</v>
+        <v>1.271231521538878</v>
       </c>
       <c r="G85">
-        <v>-7.36978329578616</v>
+        <v>-6.52892105285506</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.267628841587308</v>
       </c>
       <c r="E86">
-        <v>-23.76607218379672</v>
+        <v>-22.03120020603618</v>
       </c>
       <c r="F86">
-        <v>0.913494431700689</v>
+        <v>1.472718638391413</v>
       </c>
       <c r="G86">
-        <v>-7.364694121147462</v>
+        <v>-6.595218134463641</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.611193244729761</v>
       </c>
       <c r="E87">
-        <v>-25.01930019457544</v>
+        <v>-25.0629048707953</v>
       </c>
       <c r="F87">
-        <v>1.054832134701146</v>
+        <v>1.292969538923143</v>
       </c>
       <c r="G87">
-        <v>-7.067927318425044</v>
+        <v>-5.879061998120797</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.905683495779935</v>
       </c>
       <c r="E88">
-        <v>-25.60598211616517</v>
+        <v>-23.57000737316062</v>
       </c>
       <c r="F88">
-        <v>0.8654971676476801</v>
+        <v>1.290819097145475</v>
       </c>
       <c r="G88">
-        <v>-7.123862302348898</v>
+        <v>-6.86550547920134</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.142192650621598</v>
       </c>
       <c r="E89">
-        <v>-26.30409619766164</v>
+        <v>-27.10041023801444</v>
       </c>
       <c r="F89">
-        <v>0.7182846830265688</v>
+        <v>1.383765233209191</v>
       </c>
       <c r="G89">
-        <v>-7.339320434828275</v>
+        <v>-6.054830474617131</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.319268591035528</v>
       </c>
       <c r="E90">
-        <v>-28.27999620448043</v>
+        <v>-28.77317419475978</v>
       </c>
       <c r="F90">
-        <v>0.2533154328959838</v>
+        <v>0.6615017542994682</v>
       </c>
       <c r="G90">
-        <v>-6.824460678714246</v>
+        <v>-6.176340671406487</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.43405348193931</v>
       </c>
       <c r="E91">
-        <v>-29.00954695253815</v>
+        <v>-28.906143777047</v>
       </c>
       <c r="F91">
-        <v>0.04752577575330828</v>
+        <v>0.6384698270320308</v>
       </c>
       <c r="G91">
-        <v>-6.699560980053983</v>
+        <v>-5.43036807475297</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.486500146016795</v>
       </c>
       <c r="E92">
-        <v>-31.37909814789571</v>
+        <v>-32.01023609881874</v>
       </c>
       <c r="F92">
-        <v>-0.1732929511783587</v>
+        <v>0.1613881887377115</v>
       </c>
       <c r="G92">
-        <v>-6.594210799444891</v>
+        <v>-5.823337012376747</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.476843934675329</v>
       </c>
       <c r="E93">
-        <v>-31.88539059890127</v>
+        <v>-31.2582965752671</v>
       </c>
       <c r="F93">
-        <v>-0.3288164459517575</v>
+        <v>0.1850902652340138</v>
       </c>
       <c r="G93">
-        <v>-6.749612733721753</v>
+        <v>-5.716457782520954</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.403508721858229</v>
       </c>
       <c r="E94">
-        <v>-34.76886925244133</v>
+        <v>-35.21064679849661</v>
       </c>
       <c r="F94">
-        <v>-0.5762431622287474</v>
+        <v>-0.6358731897192699</v>
       </c>
       <c r="G94">
-        <v>-7.184108811401862</v>
+        <v>-7.03184372493583</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.268687583769851</v>
       </c>
       <c r="E95">
-        <v>-36.17738995812809</v>
+        <v>-36.69069927960853</v>
       </c>
       <c r="F95">
-        <v>-0.8005103826582688</v>
+        <v>-0.3468309518604383</v>
       </c>
       <c r="G95">
-        <v>-6.278084789521749</v>
+        <v>-6.866424221237985</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.06608006980105</v>
       </c>
       <c r="E96">
-        <v>-37.6726671688538</v>
+        <v>-37.16990239910021</v>
       </c>
       <c r="F96">
-        <v>-1.075896983881951</v>
+        <v>-0.8436906902639986</v>
       </c>
       <c r="G96">
-        <v>-7.253949612294643</v>
+        <v>-6.937469230443082</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.804629394448556</v>
       </c>
       <c r="E97">
-        <v>-39.73953516153867</v>
+        <v>-41.13643353868475</v>
       </c>
       <c r="F97">
-        <v>-1.468525737093457</v>
+        <v>-0.8201957056183963</v>
       </c>
       <c r="G97">
-        <v>-7.533220941662101</v>
+        <v>-6.798703089472605</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.472725279794486</v>
       </c>
       <c r="E98">
-        <v>-41.88854740848568</v>
+        <v>-41.36431314346173</v>
       </c>
       <c r="F98">
-        <v>-1.565158108099631</v>
+        <v>-1.039045403233609</v>
       </c>
       <c r="G98">
-        <v>-7.480255463249545</v>
+        <v>-6.367809793064765</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.095110225415449</v>
       </c>
       <c r="E99">
-        <v>-43.65170197066112</v>
+        <v>-44.90040603590619</v>
       </c>
       <c r="F99">
-        <v>-2.229026655316405</v>
+        <v>-1.658144005798681</v>
       </c>
       <c r="G99">
-        <v>-7.769760922660912</v>
+        <v>-7.482975595922325</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.648816037393468</v>
       </c>
       <c r="E100">
-        <v>-45.83002929409679</v>
+        <v>-46.99377692272095</v>
       </c>
       <c r="F100">
-        <v>-2.554964377295927</v>
+        <v>-1.310499744396201</v>
       </c>
       <c r="G100">
-        <v>-8.177075360942581</v>
+        <v>-7.604469386603884</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.192816070297446</v>
       </c>
       <c r="E101">
-        <v>-48.18778381466436</v>
+        <v>-48.40821181546173</v>
       </c>
       <c r="F101">
-        <v>-2.796517968687068</v>
+        <v>-1.976592458089492</v>
       </c>
       <c r="G101">
-        <v>-7.939879135631882</v>
+        <v>-7.286440268176264</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.653938443711562</v>
       </c>
       <c r="E102">
-        <v>-49.27915850381645</v>
+        <v>-50.70015741963134</v>
       </c>
       <c r="F102">
-        <v>-2.783317934123458</v>
+        <v>-1.91712810407953</v>
       </c>
       <c r="G102">
-        <v>-8.804494141431803</v>
+        <v>-7.811816339388314</v>
       </c>
     </row>
   </sheetData>
